--- a/task132/target/pc_relay_maintenance_compliance_2025.xlsx
+++ b/task132/target/pc_relay_maintenance_compliance_2025.xlsx
@@ -2,7 +2,6 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
@@ -10,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025 compliance" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -495,19 +494,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
         <v>3</v>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
       <c r="G4" t="n">
-        <v>94.3</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5">
@@ -522,19 +521,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D5" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>82.8</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6">
@@ -549,19 +548,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D6" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>96.2</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="7">
@@ -576,19 +575,19 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>45</v>
+      </c>
+      <c r="D7" t="n">
         <v>41</v>
       </c>
-      <c r="D7" t="n">
-        <v>35</v>
-      </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>85.40000000000001</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -603,19 +602,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="D8" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>89.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -630,19 +629,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D9" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E9" t="n">
         <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>93.2</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -657,19 +656,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D10" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>94</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="11">
@@ -684,19 +683,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D11" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>97.59999999999999</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -711,19 +710,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>85.7</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -741,16 +740,16 @@
         <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>94.3</v>
+        <v>84.90000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -765,19 +764,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>94</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="15">
@@ -792,19 +791,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>95.3</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="16">
@@ -819,19 +818,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="D16" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>88.5</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="17">
@@ -846,19 +845,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D17" t="n">
         <v>55</v>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>84.59999999999999</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="18">
@@ -873,19 +872,19 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>47</v>
+      </c>
+      <c r="D18" t="n">
         <v>46</v>
       </c>
-      <c r="D18" t="n">
-        <v>43</v>
-      </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>93.5</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -900,19 +899,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D19" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>87.8</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20">
@@ -927,19 +926,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D20" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="E20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>89.90000000000001</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="21">
@@ -954,19 +953,19 @@
         </is>
       </c>
       <c r="C21" t="n">
+        <v>64</v>
+      </c>
+      <c r="D21" t="n">
         <v>56</v>
       </c>
-      <c r="D21" t="n">
-        <v>53</v>
-      </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>94.59999999999999</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="22">
@@ -981,19 +980,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D22" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>93.90000000000001</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="23">
@@ -1008,19 +1007,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D23" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>94.3</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24">
@@ -1035,19 +1034,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D24" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>91.7</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="25">
@@ -1062,19 +1061,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D25" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>84.3</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1089,19 +1088,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D26" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="n">
         <v>0</v>
       </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
       <c r="G26" t="n">
-        <v>97.8</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -1116,19 +1115,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="D27" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>95.2</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1143,19 +1142,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="D28" t="n">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>95.7</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="29">
@@ -1170,10 +1169,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="D29" t="n">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="E29" t="n">
         <v>8</v>
@@ -1182,7 +1181,7 @@
         <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>89.2</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="30">
@@ -1197,19 +1196,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D30" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E30" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>84.59999999999999</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1224,19 +1223,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="D31" t="n">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>93.7</v>
+        <v>95.7</v>
       </c>
     </row>
   </sheetData>

--- a/task132/target/pc_relay_maintenance_compliance_2025.xlsx
+++ b/task132/target/pc_relay_maintenance_compliance_2025.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27130"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A45F68F6-4357-495F-A093-D2CBF1EECBDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_{A45F68F6-4357-495F-A093-D2CBF1EECBDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A5C68F53-9BD7-4E92-B367-9D85CC87B6ED}"/>
   </bookViews>
@@ -15,12 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="21">
   <si>
     <t>P&amp;C maintenance test compliance, calendar year 2025</t>
   </si>
   <si>
-    <t>P&amp;C maintenance programme report. Devices due a test under P&amp;C Standard 3.2: relays two-yearly at TS and three-yearly at DS, recloser controls and RTUs every year.</t>
+    <t>P&amp;C maintenance program report. Tests due: periodic test work orders raised in 2025 under P&amp;C Standard 3.2, cancelled work orders excluded. On time: done within 30 days of the due date. Status at 31 January 2026.</t>
   </si>
   <si>
     <t>Model</t>
@@ -29,52 +29,55 @@
     <t>Operating region</t>
   </si>
   <si>
-    <t>Devices due a test</t>
-  </si>
-  <si>
-    <t>Tested on time</t>
-  </si>
-  <si>
-    <t>Tested late</t>
-  </si>
-  <si>
-    <t>Not tested</t>
+    <t>Tests due</t>
+  </si>
+  <si>
+    <t>Done on time</t>
+  </si>
+  <si>
+    <t>Done late</t>
+  </si>
+  <si>
+    <t>Not done</t>
   </si>
   <si>
     <t>On-time %</t>
   </si>
   <si>
+    <t>VPR-340</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t>Central</t>
+  </si>
+  <si>
+    <t>South</t>
+  </si>
+  <si>
+    <t>VPR-220</t>
+  </si>
+  <si>
+    <t>NX-9</t>
+  </si>
+  <si>
+    <t>NX-5</t>
+  </si>
+  <si>
+    <t>KDR-30</t>
+  </si>
+  <si>
     <t>AT-7</t>
   </si>
   <si>
-    <t>North</t>
-  </si>
-  <si>
-    <t>South</t>
-  </si>
-  <si>
-    <t>KDR-30</t>
-  </si>
-  <si>
-    <t>Central</t>
-  </si>
-  <si>
-    <t>NX-5</t>
-  </si>
-  <si>
-    <t>NX-9</t>
-  </si>
-  <si>
     <t>RT-400</t>
   </si>
   <si>
     <t>RT-600</t>
   </si>
   <si>
-    <t>VPR-220</t>
-  </si>
-  <si>
-    <t>VPR-340</t>
+    <t>All models</t>
   </si>
 </sst>
 </file>
@@ -82,7 +85,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -135,11 +138,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,15 +439,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51F8671D-5156-49D2-A488-172BF59DBBC4}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="16.7109375" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
     <col min="7" max="7" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -487,19 +492,20 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>18</v>
+        <v>134</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G4" s="3">
-        <v>83.3</v>
+        <f>D4/C4</f>
+        <v>0.7164179104477612</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -510,111 +516,116 @@
         <v>11</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>162</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>127</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5" s="3">
-        <v>100</v>
+        <f>D5/C5</f>
+        <v>0.7839506172839507</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
       <c r="C6">
-        <v>11</v>
+        <v>131</v>
       </c>
       <c r="D6">
-        <v>11</v>
+        <v>99</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="3">
-        <v>100</v>
+        <f>D6/C6</f>
+        <v>0.7557251908396947</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
       </c>
       <c r="C7">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D7">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="3">
-        <v>91.7</v>
+        <f>D7/C7</f>
+        <v>0.8076923076923077</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8" s="3">
-        <v>100</v>
+        <f>D8/C8</f>
+        <v>0.9</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D9">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="3">
-        <v>95.8</v>
+        <f>D9/C9</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -625,19 +636,20 @@
         <v>10</v>
       </c>
       <c r="C10">
+        <v>36</v>
+      </c>
+      <c r="D10">
         <v>29</v>
       </c>
-      <c r="D10">
-        <v>26</v>
-      </c>
       <c r="E10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10" s="3">
-        <v>89.7</v>
+        <f>D10/C10</f>
+        <v>0.8055555555555556</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -648,42 +660,44 @@
         <v>11</v>
       </c>
       <c r="C11">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D11">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="3">
-        <v>100</v>
+        <f>D11/C11</f>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D12">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12" s="3">
-        <v>95.5</v>
+        <f>D12/C12</f>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -694,19 +708,20 @@
         <v>10</v>
       </c>
       <c r="C13">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="D13">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="3">
-        <v>91.09999999999999</v>
+        <f>D13/C13</f>
+        <v>0.9428571428571428</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -717,33 +732,34 @@
         <v>11</v>
       </c>
       <c r="C14">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D14">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14" s="3">
-        <v>93.5</v>
+        <f>D14/C14</f>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="D15">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -752,7 +768,8 @@
         <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>95.09999999999999</v>
+        <f>D15/C15</f>
+        <v>0.9047619047619048</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -763,19 +780,20 @@
         <v>10</v>
       </c>
       <c r="C16">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="D16">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16" s="3">
-        <v>98</v>
+        <f>D16/C16</f>
+        <v>0.8181818181818182</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -786,10 +804,10 @@
         <v>11</v>
       </c>
       <c r="C17">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="D17">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -798,21 +816,22 @@
         <v>1</v>
       </c>
       <c r="G17" s="3">
-        <v>94.09999999999999</v>
+        <f>D17/C17</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C18">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -821,7 +840,8 @@
         <v>1</v>
       </c>
       <c r="G18" s="3">
-        <v>77.8</v>
+        <f>D18/C18</f>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -832,19 +852,20 @@
         <v>10</v>
       </c>
       <c r="C19">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" s="3">
-        <v>75</v>
+        <f>D19/C19</f>
+        <v>0.8823529411764706</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -852,22 +873,23 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="3">
-        <v>100</v>
+        <f>D20/C20</f>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -875,22 +897,23 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C21">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="D21">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21" s="3">
-        <v>100</v>
+        <f>D21/C21</f>
+        <v>0.9130434782608695</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -898,22 +921,23 @@
         <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C22">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D22">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="3">
-        <v>90.3</v>
+        <f>D22/C22</f>
+        <v>0.8421052631578947</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -921,22 +945,23 @@
         <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G23" s="3">
-        <v>100</v>
+        <f>D23/C23</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -944,22 +969,23 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C24">
-        <v>157</v>
+        <v>3</v>
       </c>
       <c r="D24">
-        <v>142</v>
+        <v>3</v>
       </c>
       <c r="E24">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G24" s="3">
-        <v>90.40000000000001</v>
+        <f>D24/C24</f>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -967,22 +993,23 @@
         <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C25">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="D25">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="E25">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25" s="3">
-        <v>91.7</v>
+        <f>D25/C25</f>
+        <v>0.75</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -990,22 +1017,49 @@
         <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C26">
-        <v>128</v>
+        <v>4</v>
       </c>
       <c r="D26">
-        <v>117</v>
+        <v>3</v>
       </c>
       <c r="E26">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G26" s="3">
-        <v>91.40000000000001</v>
+        <f>D26/C26</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4">
+        <f>SUM(C4:C26)</f>
+        <v>796</v>
+      </c>
+      <c r="D27" s="4">
+        <f>SUM(D4:D26)</f>
+        <v>622</v>
+      </c>
+      <c r="E27" s="4">
+        <f>SUM(E4:E26)</f>
+        <v>149</v>
+      </c>
+      <c r="F27" s="4">
+        <f>SUM(F4:F26)</f>
+        <v>25</v>
+      </c>
+      <c r="G27" s="5">
+        <f>D27/C27</f>
+        <v>0.7814070351758794</v>
       </c>
     </row>
   </sheetData>

--- a/task132/target/pc_relay_maintenance_compliance_2025.xlsx
+++ b/task132/target/pc_relay_maintenance_compliance_2025.xlsx
@@ -15,12 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="24">
   <si>
     <t>P&amp;C maintenance test compliance, calendar year 2025</t>
   </si>
   <si>
-    <t>P&amp;C maintenance program report. Tests due: periodic test work orders raised in 2025 under P&amp;C Standard 3.2, cancelled work orders excluded. On time: done within 30 days of the due date. Status at 31 January 2026.</t>
+    <t>P&amp;C maintenance program report. Tests due: periodic test work orders raised in 2025 under P&amp;C Standard 3.2, cancelled work orders excluded. On time: done within 30 days of the due date. Status at 31 January 2026. Corrections made by hand are noted against the row.</t>
   </si>
   <si>
     <t>Model</t>
@@ -44,6 +44,9 @@
     <t>On-time %</t>
   </si>
   <si>
+    <t>Notes</t>
+  </si>
+  <si>
     <t>VPR-340</t>
   </si>
   <si>
@@ -59,7 +62,13 @@
     <t>VPR-220</t>
   </si>
   <si>
+    <t>1 test raised after the relay was retired, removed from due (KA 12 Feb)</t>
+  </si>
+  <si>
     <t>NX-9</t>
+  </si>
+  <si>
+    <t>1 test done on a WO raised against the breaker, moved from not done to on time (RV 9 Feb)</t>
   </si>
   <si>
     <t>NX-5</t>
@@ -439,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51F8671D-5156-49D2-A488-172BF59DBBC4}">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -449,6 +458,7 @@
     <col min="5" max="5" width="11.7109375" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" customWidth="1"/>
     <col min="7" max="7" width="11.7109375" customWidth="1"/>
+    <col min="8" max="8" width="60.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -461,7 +471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -483,115 +493,118 @@
       <c r="G3" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="H3" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>134</v>
+        <v>192</v>
       </c>
       <c r="D4">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G4" s="3">
         <f>D4/C4</f>
-        <v>0.7164179104477612</v>
+        <v>0.75520833333333337</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>162</v>
+        <v>85</v>
       </c>
       <c r="D5">
-        <v>127</v>
+        <v>59</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F5">
         <v>4</v>
       </c>
       <c r="G5" s="3">
         <f>D5/C5</f>
-        <v>0.7839506172839507</v>
+        <v>0.69411764705882351</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6">
-        <v>131</v>
+        <v>173</v>
       </c>
       <c r="D6">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="E6">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G6" s="3">
         <f>D6/C6</f>
-        <v>0.7557251908396947</v>
+        <v>0.80346820809248554</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="3">
         <f>D7/C7</f>
-        <v>0.8076923076923077</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D8">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -601,465 +614,471 @@
       </c>
       <c r="G8" s="3">
         <f>D8/C8</f>
-        <v>0.9</v>
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="H8" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
         <v>13</v>
       </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
       <c r="C9">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9" s="3">
         <f>D9/C9</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.77777777777777779</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D10">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10" s="3">
         <f>D10/C10</f>
-        <v>0.8055555555555556</v>
+        <v>0.68</v>
+      </c>
+      <c r="H10" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="D11">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="E11">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11" s="3">
         <f>D11/C11</f>
-        <v>0.6666666666666666</v>
+        <v>0.75438596491228072</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D12">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E12">
+        <v>10</v>
+      </c>
+      <c r="F12">
         <v>2</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
       </c>
       <c r="G12" s="3">
         <f>D12/C12</f>
-        <v>0.8571428571428571</v>
+        <v>0.6470588235294118</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D13">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13" s="3">
         <f>D13/C13</f>
-        <v>0.9428571428571428</v>
+        <v>0.8666666666666667</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14">
+        <v>29</v>
+      </c>
+      <c r="D14">
         <v>24</v>
       </c>
-      <c r="D14">
-        <v>16</v>
-      </c>
       <c r="E14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="3">
         <f>D14/C14</f>
-        <v>0.6666666666666666</v>
+        <v>0.82758620689655171</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D15">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="3">
         <f>D15/C15</f>
-        <v>0.9047619047619048</v>
+        <v>0.73529411764705888</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D16">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16" s="3">
         <f>D16/C16</f>
-        <v>0.8181818181818182</v>
+        <v>0.72222222222222221</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D17">
+        <v>6</v>
+      </c>
+      <c r="E17">
         <v>2</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17" s="3">
         <f>D17/C17</f>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D18">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="3">
         <f>D18/C18</f>
-        <v>0.6666666666666666</v>
+        <v>0.81818181818181823</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D19">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" s="3">
         <f>D19/C19</f>
-        <v>0.8823529411764706</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D20">
+        <v>9</v>
+      </c>
+      <c r="E20">
         <v>2</v>
-      </c>
-      <c r="E20">
-        <v>3</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20" s="3">
         <f>D20/C20</f>
-        <v>0.3333333333333333</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C21">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D21">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="3">
         <f>D21/C21</f>
-        <v>0.9130434782608695</v>
+        <v>0.70454545454545459</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C22">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D22">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E22">
         <v>5</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" s="3">
         <f>D22/C22</f>
-        <v>0.8421052631578947</v>
+        <v>0.73333333333333328</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C23">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D23">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" s="3">
         <f>D23/C23</f>
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24" s="3">
         <f>D24/C24</f>
-        <v>1</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="3">
         <f>D25/C25</f>
-        <v>0.75</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26" s="3">
         <f>D26/C26</f>
-        <v>0.75</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4">
         <f>SUM(C4:C26)</f>
-        <v>796</v>
+        <v>902</v>
       </c>
       <c r="D27" s="4">
         <f>SUM(D4:D26)</f>
-        <v>622</v>
+        <v>680</v>
       </c>
       <c r="E27" s="4">
         <f>SUM(E4:E26)</f>
-        <v>149</v>
+        <v>187</v>
       </c>
       <c r="F27" s="4">
         <f>SUM(F4:F26)</f>
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G27" s="5">
         <f>D27/C27</f>
-        <v>0.7814070351758794</v>
+        <v>0.753880266075388</v>
       </c>
     </row>
   </sheetData>
